--- a/Pipistrelli 2022.xlsx
+++ b/Pipistrelli 2022.xlsx
@@ -629,7 +629,11 @@
           <t>Sarcedo</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>45.7104304</v>
       </c>
@@ -801,7 +805,11 @@
           <t>Malo</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>45.6577546</v>
       </c>

--- a/Pipistrelli 2022.xlsx
+++ b/Pipistrelli 2022.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torri di Quartesolo</t>
+          <t>Torri di quartesolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">

--- a/Pipistrelli 2022.xlsx
+++ b/Pipistrelli 2022.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Torri di quartesolo</t>
+          <t>Torri Di Quartesolo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
